--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,6 +894,1288 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133740375</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>637802</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7033977</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133739259</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>637789</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7034033</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133739980</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>637742</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7034045</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133739428</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91932</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>637764</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7034051</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133745085</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>637936</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7034053</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133739715</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>637764</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7034042</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133739170</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>637861</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7034063</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133740033</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>637740</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7034043</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133740209</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92292</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2063</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grantickeporing</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Skeletocutis chrysella</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>637727</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7034065</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133739296</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>637791</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7034034</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133740197</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91938</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>637727</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7034065</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133740666</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>637782</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7033954</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133742410</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58822</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>637901</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7034000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -1591,50 +1591,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133740033</v>
+        <v>133740209</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>92292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2063</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637740</v>
+        <v>637727</v>
       </c>
       <c r="R11" t="n">
-        <v>7034043</v>
+        <v>7034065</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1693,45 +1688,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133740209</v>
+        <v>133740033</v>
       </c>
       <c r="B12" t="n">
-        <v>92292</v>
+        <v>57955</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2063</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637727</v>
+        <v>637740</v>
       </c>
       <c r="R12" t="n">
-        <v>7034065</v>
+        <v>7034043</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>133740375</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>133739259</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>133739428</v>
       </c>
       <c r="B7" t="n">
-        <v>91932</v>
+        <v>91934</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>133745085</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>133739170</v>
       </c>
       <c r="B10" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>133740209</v>
       </c>
       <c r="B11" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>133739296</v>
       </c>
       <c r="B13" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133740197</v>
+        <v>133740666</v>
       </c>
       <c r="B14" t="n">
-        <v>91938</v>
+        <v>57955</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,30 +1898,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637727</v>
+        <v>637782</v>
       </c>
       <c r="R14" t="n">
-        <v>7034065</v>
+        <v>7033954</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1980,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133740666</v>
+        <v>133740197</v>
       </c>
       <c r="B15" t="n">
-        <v>57955</v>
+        <v>91940</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1991,39 +2000,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637782</v>
+        <v>637727</v>
       </c>
       <c r="R15" t="n">
-        <v>7033954</v>
+        <v>7034065</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133740666</v>
+        <v>133740197</v>
       </c>
       <c r="B14" t="n">
-        <v>57955</v>
+        <v>91940</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,39 +1898,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637782</v>
+        <v>637727</v>
       </c>
       <c r="R14" t="n">
-        <v>7033954</v>
+        <v>7034065</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1989,10 +1980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133740197</v>
+        <v>133740666</v>
       </c>
       <c r="B15" t="n">
-        <v>91940</v>
+        <v>57955</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,30 +1991,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637727</v>
+        <v>637782</v>
       </c>
       <c r="R15" t="n">
-        <v>7034065</v>
+        <v>7033954</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2177,6 +2177,103 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133739376</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91885</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>637764</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7034051</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -1196,7 +1196,7 @@
         <v>133739428</v>
       </c>
       <c r="B7" t="n">
-        <v>91934</v>
+        <v>91940</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>133740209</v>
       </c>
       <c r="B11" t="n">
-        <v>92294</v>
+        <v>92300</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>133739296</v>
       </c>
       <c r="B13" t="n">
-        <v>91883</v>
+        <v>91889</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>133740197</v>
       </c>
       <c r="B14" t="n">
-        <v>91940</v>
+        <v>91946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>133739376</v>
       </c>
       <c r="B17" t="n">
-        <v>91885</v>
+        <v>91889</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -1196,7 +1196,7 @@
         <v>133739428</v>
       </c>
       <c r="B7" t="n">
-        <v>91940</v>
+        <v>91942</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1591,45 +1591,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133740209</v>
+        <v>133740033</v>
       </c>
       <c r="B11" t="n">
-        <v>92300</v>
+        <v>57955</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2063</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637727</v>
+        <v>637740</v>
       </c>
       <c r="R11" t="n">
-        <v>7034065</v>
+        <v>7034043</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1688,50 +1693,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133740033</v>
+        <v>133740209</v>
       </c>
       <c r="B12" t="n">
-        <v>57955</v>
+        <v>92302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2063</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637740</v>
+        <v>637727</v>
       </c>
       <c r="R12" t="n">
-        <v>7034043</v>
+        <v>7034065</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1793,7 +1793,7 @@
         <v>133739296</v>
       </c>
       <c r="B13" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>133740197</v>
       </c>
       <c r="B14" t="n">
-        <v>91946</v>
+        <v>91948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>133739376</v>
       </c>
       <c r="B17" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133745085</v>
+        <v>133739715</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,34 +1301,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637936</v>
+        <v>637764</v>
       </c>
       <c r="R8" t="n">
-        <v>7034053</v>
+        <v>7034042</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1361,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133739715</v>
+        <v>133745085</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,39 +1408,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637764</v>
+        <v>637936</v>
       </c>
       <c r="R9" t="n">
-        <v>7034042</v>
+        <v>7034053</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1463,11 +1468,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,50 +1591,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133740033</v>
+        <v>133740209</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>92302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2063</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637740</v>
+        <v>637727</v>
       </c>
       <c r="R11" t="n">
-        <v>7034043</v>
+        <v>7034065</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1693,45 +1688,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133740209</v>
+        <v>133740033</v>
       </c>
       <c r="B12" t="n">
-        <v>92302</v>
+        <v>57955</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2063</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637727</v>
+        <v>637740</v>
       </c>
       <c r="R12" t="n">
-        <v>7034065</v>
+        <v>7034043</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133740197</v>
+        <v>133740666</v>
       </c>
       <c r="B14" t="n">
-        <v>91948</v>
+        <v>57955</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,30 +1898,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637727</v>
+        <v>637782</v>
       </c>
       <c r="R14" t="n">
-        <v>7034065</v>
+        <v>7033954</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1980,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133740666</v>
+        <v>133740197</v>
       </c>
       <c r="B15" t="n">
-        <v>57955</v>
+        <v>91948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1991,39 +2000,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637782</v>
+        <v>637727</v>
       </c>
       <c r="R15" t="n">
-        <v>7033954</v>
+        <v>7034065</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133739715</v>
+        <v>133745085</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,39 +1301,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637764</v>
+        <v>637936</v>
       </c>
       <c r="R8" t="n">
-        <v>7034042</v>
+        <v>7034053</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1366,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133745085</v>
+        <v>133739715</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,34 +1398,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637936</v>
+        <v>637764</v>
       </c>
       <c r="R9" t="n">
-        <v>7034053</v>
+        <v>7034042</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1468,6 +1463,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,45 +1591,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133740209</v>
+        <v>133740033</v>
       </c>
       <c r="B11" t="n">
-        <v>92302</v>
+        <v>57955</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2063</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637727</v>
+        <v>637740</v>
       </c>
       <c r="R11" t="n">
-        <v>7034065</v>
+        <v>7034043</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1688,50 +1693,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133740033</v>
+        <v>133740209</v>
       </c>
       <c r="B12" t="n">
-        <v>57955</v>
+        <v>92302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2063</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637740</v>
+        <v>637727</v>
       </c>
       <c r="R12" t="n">
-        <v>7034043</v>
+        <v>7034065</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133740666</v>
+        <v>133740197</v>
       </c>
       <c r="B14" t="n">
-        <v>57955</v>
+        <v>91948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,39 +1898,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637782</v>
+        <v>637727</v>
       </c>
       <c r="R14" t="n">
-        <v>7033954</v>
+        <v>7034065</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1989,10 +1980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133740197</v>
+        <v>133740666</v>
       </c>
       <c r="B15" t="n">
-        <v>91948</v>
+        <v>57955</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,30 +1991,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637727</v>
+        <v>637782</v>
       </c>
       <c r="R15" t="n">
-        <v>7034065</v>
+        <v>7033954</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -1591,50 +1591,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133740033</v>
+        <v>133740209</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>92302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2063</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637740</v>
+        <v>637727</v>
       </c>
       <c r="R11" t="n">
-        <v>7034043</v>
+        <v>7034065</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1693,45 +1688,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133740209</v>
+        <v>133740033</v>
       </c>
       <c r="B12" t="n">
-        <v>92302</v>
+        <v>57955</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2063</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637727</v>
+        <v>637740</v>
       </c>
       <c r="R12" t="n">
-        <v>7034065</v>
+        <v>7034043</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133740197</v>
+        <v>133740666</v>
       </c>
       <c r="B14" t="n">
-        <v>91948</v>
+        <v>57955</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,30 +1898,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637727</v>
+        <v>637782</v>
       </c>
       <c r="R14" t="n">
-        <v>7034065</v>
+        <v>7033954</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1980,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133740666</v>
+        <v>133740197</v>
       </c>
       <c r="B15" t="n">
-        <v>57955</v>
+        <v>91948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1991,39 +2000,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637782</v>
+        <v>637727</v>
       </c>
       <c r="R15" t="n">
-        <v>7033954</v>
+        <v>7034065</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133745085</v>
+        <v>133739715</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,34 +1301,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637936</v>
+        <v>637764</v>
       </c>
       <c r="R8" t="n">
-        <v>7034053</v>
+        <v>7034042</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1361,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133739715</v>
+        <v>133745085</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,39 +1408,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637764</v>
+        <v>637936</v>
       </c>
       <c r="R9" t="n">
-        <v>7034042</v>
+        <v>7034053</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1463,11 +1468,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,45 +1591,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133740209</v>
+        <v>133740033</v>
       </c>
       <c r="B11" t="n">
-        <v>92302</v>
+        <v>57955</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2063</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637727</v>
+        <v>637740</v>
       </c>
       <c r="R11" t="n">
-        <v>7034065</v>
+        <v>7034043</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1688,50 +1693,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133740033</v>
+        <v>133740209</v>
       </c>
       <c r="B12" t="n">
-        <v>57955</v>
+        <v>92302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2063</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637740</v>
+        <v>637727</v>
       </c>
       <c r="R12" t="n">
-        <v>7034043</v>
+        <v>7034065</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133740666</v>
+        <v>133740197</v>
       </c>
       <c r="B14" t="n">
-        <v>57955</v>
+        <v>91948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,39 +1898,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637782</v>
+        <v>637727</v>
       </c>
       <c r="R14" t="n">
-        <v>7033954</v>
+        <v>7034065</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1989,10 +1980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133740197</v>
+        <v>133740666</v>
       </c>
       <c r="B15" t="n">
-        <v>91948</v>
+        <v>57955</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,30 +1991,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637727</v>
+        <v>637782</v>
       </c>
       <c r="R15" t="n">
-        <v>7034065</v>
+        <v>7033954</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>133740375</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>133739259</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>133739980</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>133739428</v>
       </c>
       <c r="B7" t="n">
-        <v>91942</v>
+        <v>91961</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>133739715</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>133745085</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>133739170</v>
       </c>
       <c r="B10" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,50 +1591,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133740033</v>
+        <v>133740209</v>
       </c>
       <c r="B11" t="n">
-        <v>57955</v>
+        <v>92293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>2063</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637740</v>
+        <v>637727</v>
       </c>
       <c r="R11" t="n">
-        <v>7034043</v>
+        <v>7034065</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1693,45 +1688,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133740209</v>
+        <v>133740033</v>
       </c>
       <c r="B12" t="n">
-        <v>92302</v>
+        <v>57962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2063</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637727</v>
+        <v>637740</v>
       </c>
       <c r="R12" t="n">
-        <v>7034065</v>
+        <v>7034043</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1793,7 +1793,7 @@
         <v>133739296</v>
       </c>
       <c r="B13" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>133740197</v>
       </c>
       <c r="B14" t="n">
-        <v>91948</v>
+        <v>91967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>133740666</v>
       </c>
       <c r="B15" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>133742410</v>
       </c>
       <c r="B16" t="n">
-        <v>58822</v>
+        <v>58829</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>133739376</v>
       </c>
       <c r="B17" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133739715</v>
+        <v>133745085</v>
       </c>
       <c r="B8" t="n">
-        <v>57965</v>
+        <v>79348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,39 +1301,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637764</v>
+        <v>637936</v>
       </c>
       <c r="R8" t="n">
-        <v>7034042</v>
+        <v>7034053</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1366,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133745085</v>
+        <v>133739715</v>
       </c>
       <c r="B9" t="n">
-        <v>79348</v>
+        <v>57965</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,34 +1398,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637936</v>
+        <v>637764</v>
       </c>
       <c r="R9" t="n">
-        <v>7034053</v>
+        <v>7034042</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1468,6 +1463,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133740197</v>
+        <v>133740666</v>
       </c>
       <c r="B14" t="n">
-        <v>91967</v>
+        <v>57962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,30 +1898,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637727</v>
+        <v>637782</v>
       </c>
       <c r="R14" t="n">
-        <v>7034065</v>
+        <v>7033954</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1980,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133740666</v>
+        <v>133740197</v>
       </c>
       <c r="B15" t="n">
-        <v>57962</v>
+        <v>91967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1991,39 +2000,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637782</v>
+        <v>637727</v>
       </c>
       <c r="R15" t="n">
-        <v>7033954</v>
+        <v>7034065</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>133740375</v>
       </c>
       <c r="B4" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>133739259</v>
       </c>
       <c r="B5" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>133739980</v>
       </c>
       <c r="B6" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>133739428</v>
       </c>
       <c r="B7" t="n">
-        <v>91961</v>
+        <v>91971</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133745085</v>
+        <v>133739715</v>
       </c>
       <c r="B8" t="n">
-        <v>79348</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,34 +1301,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637936</v>
+        <v>637764</v>
       </c>
       <c r="R8" t="n">
-        <v>7034053</v>
+        <v>7034042</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1361,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133739715</v>
+        <v>133745085</v>
       </c>
       <c r="B9" t="n">
-        <v>57965</v>
+        <v>79358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,39 +1408,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637764</v>
+        <v>637936</v>
       </c>
       <c r="R9" t="n">
-        <v>7034042</v>
+        <v>7034053</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1463,11 +1468,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1497,7 +1497,7 @@
         <v>133739170</v>
       </c>
       <c r="B10" t="n">
-        <v>79348</v>
+        <v>79358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,45 +1591,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133740209</v>
+        <v>133740033</v>
       </c>
       <c r="B11" t="n">
-        <v>92293</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2063</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637727</v>
+        <v>637740</v>
       </c>
       <c r="R11" t="n">
-        <v>7034065</v>
+        <v>7034043</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1688,50 +1693,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133740033</v>
+        <v>133740209</v>
       </c>
       <c r="B12" t="n">
-        <v>57962</v>
+        <v>92303</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>2063</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637740</v>
+        <v>637727</v>
       </c>
       <c r="R12" t="n">
-        <v>7034043</v>
+        <v>7034065</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1793,7 +1793,7 @@
         <v>133739296</v>
       </c>
       <c r="B13" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>133740666</v>
       </c>
       <c r="B14" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>133740197</v>
       </c>
       <c r="B15" t="n">
-        <v>91967</v>
+        <v>91977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>133742410</v>
       </c>
       <c r="B16" t="n">
-        <v>58829</v>
+        <v>58839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>133739376</v>
       </c>
       <c r="B17" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133739715</v>
+        <v>133745085</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,39 +1301,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637764</v>
+        <v>637936</v>
       </c>
       <c r="R8" t="n">
-        <v>7034042</v>
+        <v>7034053</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1366,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133745085</v>
+        <v>133739715</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,34 +1398,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637936</v>
+        <v>637764</v>
       </c>
       <c r="R9" t="n">
-        <v>7034053</v>
+        <v>7034042</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1468,6 +1463,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133740666</v>
+        <v>133740197</v>
       </c>
       <c r="B14" t="n">
-        <v>57972</v>
+        <v>91977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,39 +1898,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637782</v>
+        <v>637727</v>
       </c>
       <c r="R14" t="n">
-        <v>7033954</v>
+        <v>7034065</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1989,10 +1980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133740197</v>
+        <v>133740666</v>
       </c>
       <c r="B15" t="n">
-        <v>91977</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,30 +1991,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637727</v>
+        <v>637782</v>
       </c>
       <c r="R15" t="n">
-        <v>7034065</v>
+        <v>7033954</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133745085</v>
+        <v>133739715</v>
       </c>
       <c r="B8" t="n">
-        <v>79358</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,34 +1301,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637936</v>
+        <v>637764</v>
       </c>
       <c r="R8" t="n">
-        <v>7034053</v>
+        <v>7034042</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1361,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133739715</v>
+        <v>133745085</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>79358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1398,39 +1408,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637764</v>
+        <v>637936</v>
       </c>
       <c r="R9" t="n">
-        <v>7034042</v>
+        <v>7034053</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1463,11 +1468,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133740197</v>
+        <v>133740666</v>
       </c>
       <c r="B14" t="n">
-        <v>91977</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,30 +1898,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637727</v>
+        <v>637782</v>
       </c>
       <c r="R14" t="n">
-        <v>7034065</v>
+        <v>7033954</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1980,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133740666</v>
+        <v>133740197</v>
       </c>
       <c r="B15" t="n">
-        <v>57972</v>
+        <v>91977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1991,39 +2000,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637782</v>
+        <v>637727</v>
       </c>
       <c r="R15" t="n">
-        <v>7033954</v>
+        <v>7034065</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133740666</v>
+        <v>133740197</v>
       </c>
       <c r="B14" t="n">
-        <v>57972</v>
+        <v>91977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,39 +1898,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637782</v>
+        <v>637727</v>
       </c>
       <c r="R14" t="n">
-        <v>7033954</v>
+        <v>7034065</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1989,10 +1980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133740197</v>
+        <v>133740666</v>
       </c>
       <c r="B15" t="n">
-        <v>91977</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2000,30 +1991,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637727</v>
+        <v>637782</v>
       </c>
       <c r="R15" t="n">
-        <v>7034065</v>
+        <v>7033954</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133740197</v>
+        <v>133740666</v>
       </c>
       <c r="B14" t="n">
-        <v>91977</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,30 +1898,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637727</v>
+        <v>637782</v>
       </c>
       <c r="R14" t="n">
-        <v>7034065</v>
+        <v>7033954</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1980,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133740666</v>
+        <v>133740197</v>
       </c>
       <c r="B15" t="n">
-        <v>57972</v>
+        <v>91977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1991,39 +2000,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637782</v>
+        <v>637727</v>
       </c>
       <c r="R15" t="n">
-        <v>7033954</v>
+        <v>7034065</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>133740375</v>
       </c>
       <c r="B4" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>133739259</v>
       </c>
       <c r="B5" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>133739428</v>
       </c>
       <c r="B7" t="n">
-        <v>91971</v>
+        <v>91973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>133745085</v>
       </c>
       <c r="B9" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>133739170</v>
       </c>
       <c r="B10" t="n">
-        <v>79358</v>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>133740209</v>
       </c>
       <c r="B12" t="n">
-        <v>92303</v>
+        <v>92305</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>133739296</v>
       </c>
       <c r="B13" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133740197</v>
+        <v>133740666</v>
       </c>
       <c r="B14" t="n">
-        <v>91977</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,30 +1898,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>637727</v>
+        <v>637782</v>
       </c>
       <c r="R14" t="n">
-        <v>7034065</v>
+        <v>7033954</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1980,10 +1989,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133740666</v>
+        <v>133740197</v>
       </c>
       <c r="B15" t="n">
-        <v>57972</v>
+        <v>91979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1991,39 +2000,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637782</v>
+        <v>637727</v>
       </c>
       <c r="R15" t="n">
-        <v>7033954</v>
+        <v>7034065</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2182,7 +2182,7 @@
         <v>133739376</v>
       </c>
       <c r="B17" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -1290,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133739715</v>
+        <v>133745085</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1301,39 +1301,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637764</v>
+        <v>637936</v>
       </c>
       <c r="R8" t="n">
-        <v>7034042</v>
+        <v>7034053</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1366,11 +1361,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1397,10 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133745085</v>
+        <v>133739715</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,34 +1398,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjärdalsmyran, Tjärdalsmyran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637936</v>
+        <v>637764</v>
       </c>
       <c r="R9" t="n">
-        <v>7034053</v>
+        <v>7034042</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1468,6 +1463,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 21981-2026 artfynd.xlsx
+++ b/artfynd/A 21981-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133739428</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133740209</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133739296</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133739376</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712680</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712683</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133739170</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133739259</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133740375</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133745085</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1762,6 +1817,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661890</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661891</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1966,6 +2031,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661892</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2063,6 +2133,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661896</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2160,6 +2235,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661897</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2257,6 +2337,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661898</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2354,6 +2439,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661899</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2451,6 +2541,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661900</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2548,6 +2643,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661901</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2645,6 +2745,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661902</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2742,6 +2847,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661903</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2839,6 +2949,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661904</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2936,6 +3051,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661905</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3038,6 +3158,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133739980</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3140,6 +3265,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133740033</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3242,6 +3372,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133740666</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3349,6 +3484,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133739715</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3456,6 +3596,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133740878</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3558,6 +3703,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661882</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3655,6 +3805,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661887</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3761,6 +3916,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113712682</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3858,6 +4018,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133742410</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3955,8 +4120,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134661908</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>